--- a/Zeitplan.xlsx
+++ b/Zeitplan.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oCloud\Home-Cloud\Lehre\BIBB\BIBB_R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263B02C8-9119-440A-8010-1ED13AAD8875}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEB87B3-E45A-4A5B-BD2C-9168E952F3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5145" yWindow="4425" windowWidth="23655" windowHeight="12855" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -176,9 +176,6 @@
     <t>Zusammenfassung, Ausblick zur eigenen Vertiefung (Dashboards bauen, Animationen erstellen), weiterführende Ressourcen</t>
   </si>
   <si>
-    <t>Gewichtung, Einstieg in Inferenzstatistik (Konfidenzintervalle)</t>
-  </si>
-  <si>
     <t>Variablen erstellen Teil 2 (Infos aus Variablen kombinieren, gruppierte Operationen)</t>
   </si>
   <si>
@@ -201,6 +198,9 @@
   </si>
   <si>
     <t>Ergebnisexport Teil 2 oder Wunschthema, bspw. weitere Datenaufbereitung</t>
+  </si>
+  <si>
+    <t>Gewichtung, Einstieg in Inferenzstatistik (t-Tests)</t>
   </si>
 </sst>
 </file>
@@ -1540,7 +1540,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" s="1">
         <f>D9-C9</f>
@@ -1571,7 +1571,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="1">
         <f>D11-C11</f>
@@ -1612,7 +1612,7 @@
         <v>0.5</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F13" s="1">
         <f>D13-C13</f>
@@ -1623,7 +1623,7 @@
         <v>0.34374999999999989</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E15" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="F15" s="1">
         <f>D15-C15</f>
@@ -1696,7 +1696,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F17" s="1">
         <f>D17-C17</f>
@@ -1839,7 +1839,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F25" s="1">
         <f>D25-C25</f>
@@ -1864,7 +1864,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F27" s="1">
         <f>D27-C27</f>
@@ -1942,7 +1942,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E31" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F31" s="1">
         <f>D31-C31</f>

--- a/Zeitplan.xlsx
+++ b/Zeitplan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\oCloud\Home-Cloud\Lehre\BIBB\BIBB_R\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FEB87B3-E45A-4A5B-BD2C-9168E952F3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232A9389-6E57-4DD7-9593-3B7DD94D8EBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5145" yWindow="4425" windowWidth="23655" windowHeight="12855" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23655" yWindow="4425" windowWidth="23655" windowHeight="12855" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -164,24 +164,12 @@
     <t>Deskriptionen: erste Visualisierungen mit ggplot2</t>
   </si>
   <si>
-    <t>Regressionsanalyse Teil 2 (Annahmen &amp; log. Regression, AME)</t>
-  </si>
-  <si>
-    <t>Recap Woche 1, Einstieg in die Regressionsanalyse</t>
-  </si>
-  <si>
-    <t>Regressionsergebnisse visualisieren mit ggplot2 (adjusted predictions)</t>
-  </si>
-  <si>
     <t>Zusammenfassung, Ausblick zur eigenen Vertiefung (Dashboards bauen, Animationen erstellen), weiterführende Ressourcen</t>
   </si>
   <si>
     <t>Variablen erstellen Teil 2 (Infos aus Variablen kombinieren, gruppierte Operationen)</t>
   </si>
   <si>
-    <t>Zusammenfassung, ggf. weitere Modelle - zB fixed effects mit fixest</t>
-  </si>
-  <si>
     <t>filter/select</t>
   </si>
   <si>
@@ -201,6 +189,18 @@
   </si>
   <si>
     <t>Gewichtung, Einstieg in Inferenzstatistik (t-Tests)</t>
+  </si>
+  <si>
+    <t>Recap Woche 1, Regressionsanalyse in R</t>
+  </si>
+  <si>
+    <t>Regressionsanalyse Teil 2 - Erweiterungen: Standardfehler, Fixed Effects</t>
+  </si>
+  <si>
+    <t>Regressionsanalyse Teil 3 - logistische Regression, AMEs, …</t>
+  </si>
+  <si>
+    <t>Zusammenfassung, ggf. weitere Modelle</t>
   </si>
 </sst>
 </file>
@@ -1540,7 +1540,7 @@
         <v>0.63541666666666663</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F9" s="1">
         <f>D9-C9</f>
@@ -1571,7 +1571,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1">
         <f>D11-C11</f>
@@ -1612,7 +1612,7 @@
         <v>0.5</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F13" s="1">
         <f>D13-C13</f>
@@ -1623,7 +1623,7 @@
         <v>0.34374999999999989</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -1655,7 +1655,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E15" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1">
         <f>D15-C15</f>
@@ -1696,7 +1696,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E17" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F17" s="1">
         <f>D17-C17</f>
@@ -1722,7 +1722,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E19" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F19" s="1">
         <f>D19-C19</f>
@@ -1761,7 +1761,7 @@
         <v>0.5</v>
       </c>
       <c r="E21" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="F21" s="1">
         <f>D21-C21</f>
@@ -1800,7 +1800,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E23" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="F23" s="1">
         <f>D23-C23</f>
@@ -1839,7 +1839,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F25" s="1">
         <f>D25-C25</f>
@@ -1864,7 +1864,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="E27" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F27" s="1">
         <f>D27-C27</f>
@@ -1942,7 +1942,7 @@
         <v>0.60416666666666663</v>
       </c>
       <c r="E31" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F31" s="1">
         <f>D31-C31</f>
@@ -1981,7 +1981,7 @@
         <v>0.64583333333333337</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F33" s="1">
         <f>D33-C33</f>
